--- a/output/full_scan/batch_seq8_2026-10-05.xlsx
+++ b/output/full_scan/batch_seq8_2026-10-05.xlsx
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>973.7305767311088</v>
+        <v>1143.730576731109</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>249</v>
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>70.91596564768422</v>
+        <v>70.91596552646332</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>35.23581228888698</v>
+        <v>35.23581229889069</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>2.629674884068115</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>2.075747757123592</v>
+        <v>2.075747756567274</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6983</v>
+        <v>8021</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>華洋精機</t>
+          <t>尖點</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>973.5792098557752</v>
+        <v>1096.949291789002</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>359.5</v>
+        <v>560</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,29 +605,29 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>63.1263660166689</v>
+        <v>74.8094421775466</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>25.27544030190486</v>
+        <v>18.7158574112719</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>3.223632876092597</v>
+        <v>2.11201346605112</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>-0.3905721053931188</v>
+        <v>10.0387911670853</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, invest_trust_buy_2d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>894</v>
+        <v>1064</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>300</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>75.8338817575046</v>
+        <v>75.83388163833237</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>30.1157236910859</v>
+        <v>30.11572372467428</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>6.974702139900685</v>
@@ -676,11 +676,11 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>3.403055775226824</v>
+        <v>3.403055776117013</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>875.9203152106383</v>
+        <v>1015.920315210638</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>176</v>
@@ -711,7 +711,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>68.76415144142595</v>
+        <v>68.76415143070852</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>27.36531364285793</v>
@@ -733,27 +733,27 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>7703</v>
+        <v>6983</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>銳澤</t>
+          <t>華洋精機</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>868.1834478759076</v>
+        <v>973.5792098557744</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>205.5</v>
+        <v>359.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>63.0026951898744</v>
+        <v>63.12636597627043</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>31.53194358287507</v>
+        <v>25.27544031088262</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.613320359976589</v>
+        <v>3.223632876092597</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.0115898267596392</v>
+        <v>-0.3905721048367594</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6953</v>
+        <v>6957</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>家碩</t>
+          <t>裕慶-KY</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>784</v>
+        <v>959.0278087330594</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>257.5</v>
+        <v>410</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>66.42526401295555</v>
+        <v>88.19116441644212</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>19.9437417814623</v>
+        <v>51.77176078987296</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>5.364330875511537</v>
+        <v>2.002780873305926</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>2.082896538248161</v>
+        <v>13.81837434860595</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6859</v>
+        <v>6953</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>伯特光</t>
+          <t>家碩</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>766.0091962718794</v>
+        <v>954</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>123</v>
+        <v>257.5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>62.3745570507924</v>
+        <v>66.42526397828023</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>40.56736575742436</v>
+        <v>19.94374180196074</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.072823410187611</v>
+        <v>5.364330875511537</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.0136080632516111</v>
+        <v>2.082896538915807</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6870</v>
+        <v>7788</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>騰雲</t>
+          <t>松川精密</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>765.5168922854842</v>
+        <v>947.099155138883</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>320</v>
+        <v>332.5</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>57.15549753010396</v>
+        <v>65.5856805783082</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>34.37677977695972</v>
+        <v>18.02815231490145</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.3677819219919679</v>
+        <v>1.433341547445417</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>2</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>-1.173593792566674</v>
+        <v>1.054367416593045</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, stronger_than_market, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6903</v>
+        <v>6944</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>巨漢</t>
+          <t>兆聯實業</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>747.6898942519994</v>
+        <v>906.8710356255062</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>328</v>
+        <v>814</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>61.6272476695844</v>
+        <v>71.0241045662539</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>14.17930689349124</v>
+        <v>24.92688903220587</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>2.12439576612553</v>
+        <v>1.548918375283402</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>3.436350425225044</v>
+        <v>14.96494413313206</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6895</v>
+        <v>6901</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>宏碩系統</t>
+          <t>鑽石投資</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>718.7209471430164</v>
+        <v>903.489900021258</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>156.5</v>
+        <v>18</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>63.39493275152721</v>
+        <v>68.41241433885955</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>15.62230419906576</v>
+        <v>21.57438535057933</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>3.496551277717442</v>
+        <v>3.750020847163833</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.1188171198986651</v>
+        <v>0.3175787997344613</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, foreign_buy_3d, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>7788</v>
+        <v>6903</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>松川精密</t>
+          <t>巨漢</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>717.099155138883</v>
+        <v>887.6898942519986</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>332.5</v>
+        <v>328</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>65.58568058610997</v>
+        <v>61.62724769542567</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>18.02815231553375</v>
+        <v>14.17930686394067</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.433341547445417</v>
+        <v>2.12439576612553</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>1.05436741592542</v>
+        <v>3.436350424779968</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>7717</v>
+        <v>7795</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>萊德光電-KY</t>
+          <t>長廣</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>703.4784522860308</v>
+        <v>869.2310375548577</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>592</v>
+        <v>559</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>61.37123976986931</v>
+        <v>60.99523728047696</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>17.88089212083084</v>
+        <v>19.62002817799258</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.9768467742953156</v>
+        <v>1.016946882413917</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-0.8118331792226101</v>
+        <v>6.098758265584535</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>8021</v>
+        <v>7711</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>尖點</t>
+          <t>永擎</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>691.9492917890014</v>
+        <v>869.226322909942</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>560</v>
+        <v>634</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>74.809442174558</v>
+        <v>64.61607090508721</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>18.71585742087198</v>
+        <v>28.25009381817668</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>2.11201346605112</v>
+        <v>1.290314147471747</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>10.03879116652897</v>
+        <v>3.414437452117163</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6937</v>
+        <v>7703</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>天虹</t>
+          <t>銳澤</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>687.8053053743026</v>
+        <v>868.1834478759075</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>302.5</v>
+        <v>205.5</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>57.52517130145253</v>
+        <v>63.00269509277297</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>28.71715511782915</v>
+        <v>31.53194363112808</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.6643058835520319</v>
+        <v>0.613320359976589</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.180146064399187</v>
+        <v>0.0115898284287165</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6901</v>
+        <v>8016</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>鑽石投資</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>683.489900021258</v>
+        <v>860.0040462379901</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>18</v>
+        <v>293.5</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,49 +1294,49 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>68.41241432495714</v>
+        <v>57.55211589734172</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>21.57438549069122</v>
+        <v>10.33054206082707</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>3.750020847163833</v>
+        <v>0.9078100435730336</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.3175787997233346</v>
+        <v>1.99093197311333</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, invest_trust_buy_2d, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>7772</v>
+        <v>6895</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>耀穎</t>
+          <t>宏碩系統</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>673.2958998525121</v>
+        <v>858.7209471430162</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>167.5</v>
+        <v>156.5</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>61.41740226183406</v>
+        <v>63.39493224605705</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>57.46657311113527</v>
+        <v>15.62230453342169</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>2.365822353922162</v>
+        <v>3.496551277717442</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>1.255750537506451</v>
+        <v>0.1188171247945946</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, foreign_buy_3d, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6944</v>
+        <v>6962</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>兆聯實業</t>
+          <t>奕力-KY</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>656.8710356255065</v>
+        <v>830.3910666455547</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>814</v>
+        <v>33.9</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>71.02410459370195</v>
+        <v>68.51016240852513</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>24.92688903220587</v>
+        <v>16.55825626976338</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.548918375283402</v>
+        <v>2.099495234292567</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>14.96494413246445</v>
+        <v>0.3495624905724732</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6933</v>
+        <v>7730</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>AMAX-KY</t>
+          <t>暉盛-創</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>647.1720673568191</v>
+        <v>827.8613567677071</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>384</v>
+        <v>188</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>65.87806044717695</v>
+        <v>60.16356804776326</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45.23027539558454</v>
+        <v>26.16476875949396</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.081338093228143</v>
+        <v>1.101010577059025</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.9520651940392568</v>
+        <v>1.721109608348501</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>7711</v>
+        <v>6859</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>永擎</t>
+          <t>伯特光</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>639.226322909942</v>
+        <v>766.0091962718798</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>634</v>
+        <v>123</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>64.61607090039877</v>
+        <v>62.37455718550816</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>28.25009381227452</v>
+        <v>40.56736574589923</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.290314147471747</v>
+        <v>1.072823410187611</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>3.414437453229894</v>
+        <v>0.0136080624727186</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6957</v>
+        <v>6870</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>裕慶-KY</t>
+          <t>騰雲</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>639.0278087330593</v>
+        <v>765.5168922854843</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>410</v>
+        <v>320</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>88.19116442462062</v>
+        <v>57.15549744893139</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>51.77176077213088</v>
+        <v>34.37677997566277</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>2.002780873305926</v>
+        <v>0.3677819219919679</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,11 +1577,11 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>13.81837434905101</v>
+        <v>-1.17359379078632</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>618.7482830915152</v>
+        <v>758.7482830915151</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>1605</v>
@@ -1612,10 +1612,10 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>55.74032337345471</v>
+        <v>55.74032336597337</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>14.93134313441624</v>
+        <v>14.93134315850042</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>0.6778336213124949</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>15.61222086709606</v>
+        <v>15.6122208676525</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>7827</v>
+        <v>6916</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>漢康-KY創</t>
+          <t>華凌</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>614.187721825835</v>
+        <v>741.4448158253227</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>167.5</v>
+        <v>19.05</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>67.72201828276246</v>
+        <v>58.91127512032174</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>16.06703282594501</v>
+        <v>20.04570227046039</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.218772182583495</v>
+        <v>2.372123478411789</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>1.292880439037818</v>
+        <v>0.09334678572619751</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6916</v>
+        <v>7827</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>華凌</t>
+          <t>漢康-KY創</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>606.4448158253231</v>
+        <v>724.187721825835</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>19.05</v>
+        <v>167.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>58.91127528240922</v>
+        <v>67.72201850246202</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>20.0457022194221</v>
+        <v>16.06703284956526</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>2.372123478411789</v>
+        <v>1.218772182583495</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.0933467857707025</v>
+        <v>1.292880437747085</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6902</v>
+        <v>6861</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>GOGOLOOK</t>
+          <t>睿生光電</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>606.2678914475168</v>
+        <v>718.3094744238855</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>147.5</v>
+        <v>295.5</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>53.88927301898342</v>
+        <v>67.96082502230394</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>31.60383391906294</v>
+        <v>38.86658172174923</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.853147516764868</v>
+        <v>0.7470208874308065</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.3570541708452248</v>
+        <v>7.151063811381494</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6924</v>
+        <v>7799</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>榮惠-KY創</t>
+          <t>禾榮科</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>592.3587838927726</v>
+        <v>705.1851199708984</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>132.5</v>
+        <v>537</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>55.4068553410068</v>
+        <v>66.63883227538408</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>31.46963391061105</v>
+        <v>45.43898119641759</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.6112044372017812</v>
+        <v>0.5505366778106704</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.6946619548685167</v>
+        <v>5.569118067465276</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6922</v>
+        <v>7717</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>宸曜</t>
+          <t>萊德光電-KY</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>589.2985228199036</v>
+        <v>703.4784522860308</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>215</v>
+        <v>592</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>58.52377660315612</v>
+        <v>61.37123976986931</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>24.87031065675979</v>
+        <v>17.88089212083084</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.844949395638401</v>
+        <v>0.9768467742953156</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>2.105147218048852</v>
+        <v>-0.8118331792226101</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>7744</v>
+        <v>6924</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>崴寶</t>
+          <t>榮惠-KY創</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>589.0463661216098</v>
+        <v>702.3587838927726</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>528</v>
+        <v>132.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>54.51636071710992</v>
+        <v>55.40685532547781</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>27.73636351961937</v>
+        <v>31.46963390222651</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.4943394673588457</v>
+        <v>0.6112044372017812</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.8090420978232693</v>
+        <v>-0.6946619546904831</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6962</v>
+        <v>8028</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>奕力-KY</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>580.3910666455546</v>
+        <v>693.592838528791</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>33.9</v>
+        <v>281.5</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>68.51016242166689</v>
+        <v>61.8468163177253</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>16.55825623290185</v>
+        <v>25.29100942442932</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>2.099495234292567</v>
+        <v>0.902035677019093</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.3495624904500725</v>
+        <v>5.181646709879908</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>8028</v>
+        <v>6967</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
+          <t>汎瑋材料</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>578.5928385287912</v>
+        <v>692.0630637882527</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>281.5</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>61.84681636347138</v>
+        <v>57.99071725787219</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>25.29100929412571</v>
+        <v>14.42747023806271</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.902035677019093</v>
+        <v>0.7294244357015111</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>5.181646709879908</v>
+        <v>0.7492054690826635</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, foreign_buy_3d, stronger_than_market, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6861</v>
+        <v>6937</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>睿生光電</t>
+          <t>天虹</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>578.3094744238857</v>
+        <v>687.8053053743026</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>295.5</v>
+        <v>302.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>67.96082502367676</v>
+        <v>57.52517133548388</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>38.8665817194275</v>
+        <v>28.71715516299812</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.7470208874308065</v>
+        <v>0.6643058835520319</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>7.151063811025431</v>
+        <v>0.180146064510474</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>7736</v>
+        <v>7772</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>虎山</t>
+          <t>耀穎</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>575.1000546595033</v>
+        <v>673.2958998525121</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>71</v>
+        <v>167.5</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>61.10828216065207</v>
+        <v>61.41740225288078</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>19.93416097884933</v>
+        <v>57.46657311113525</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>5.887445329760578</v>
+        <v>2.365822353922162</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.2130554462039311</v>
+        <v>1.255750537662223</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>7799</v>
+        <v>6933</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>禾榮科</t>
+          <t>AMAX-KY</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>565.1851199708984</v>
+        <v>647.1720673568191</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>537</v>
+        <v>384</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>66.63883216390246</v>
+        <v>65.87806053566106</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45.43898117042555</v>
+        <v>45.23027544306831</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.5505366778106704</v>
+        <v>1.081338093228143</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>5.569118073028818</v>
+        <v>0.9520651898109094</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>7795</v>
+        <v>6877</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>長廣</t>
+          <t>鏵友益</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>559.2310375548577</v>
+        <v>617.3598869059585</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>559</v>
+        <v>145.5</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>60.99523725884845</v>
+        <v>67.5095561312598</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>19.62002816798352</v>
+        <v>25.53772620770279</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.016946882413917</v>
+        <v>7.226308264503901</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>6.098758265695801</v>
+        <v>3.606732784767401</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6967</v>
+        <v>6902</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>汎瑋材料</t>
+          <t>GOGOLOOK</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>552.0630637882526</v>
+        <v>606.2678914475168</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>70.90000000000001</v>
+        <v>147.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>57.99071726095828</v>
+        <v>53.88927299654585</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>14.42747023524482</v>
+        <v>31.60383397806375</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.7294244357015111</v>
+        <v>0.853147516764868</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.7492054691271657</v>
+        <v>0.3570541712680484</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, foreign_buy_3d, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>7730</v>
+        <v>6907</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>暉盛-創</t>
+          <t>雅特力-KY</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>547.8613567677072</v>
+        <v>606.138142401401</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>188</v>
+        <v>193.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>60.16356807062163</v>
+        <v>54.40868112294999</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>26.16476869833906</v>
+        <v>17.03882811821394</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.101010577059025</v>
+        <v>1.168880686132186</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>1.721109608014675</v>
+        <v>1.410241633802185</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6885</v>
+        <v>7750</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>全福生技</t>
+          <t>新代</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>541.5986477092932</v>
+        <v>590.2771295109974</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>29.3</v>
+        <v>2070</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,49 +2407,49 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>57.22410349492465</v>
+        <v>50.6484405594046</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>57.97306775946776</v>
+        <v>19.02153799812208</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.912802479979175</v>
+        <v>1.356261168170537</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.1266333037523286</v>
+        <v>6.490956347409735</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, stronger_than_market, dealer_buy_3d, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6925</v>
+        <v>6922</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>意藍</t>
+          <t>宸曜</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>540.367050905416</v>
+        <v>589.2985228199036</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>69.2</v>
+        <v>215</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>64.91246064449626</v>
+        <v>58.52377666431028</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>36.04300896439051</v>
+        <v>24.87031064601276</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.478664261791016</v>
+        <v>0.844949395638401</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>1.334178409898683</v>
+        <v>2.105147217715053</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>8016</v>
+        <v>7744</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>崴寶</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>540.00404623799</v>
+        <v>589.0463661216099</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>293.5</v>
+        <v>528</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>57.5521159252942</v>
+        <v>54.51636090976879</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>10.33054207646795</v>
+        <v>27.73636354914312</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.9078100435730336</v>
+        <v>0.4943394673588457</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>1.990931972668218</v>
+        <v>-0.8090420992697887</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>7749</v>
+        <v>6947</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>意騰-KY</t>
+          <t>台鎔科技</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>520.3544650161869</v>
+        <v>579.0101026347423</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>399</v>
+        <v>68.7</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>62.30496584726836</v>
+        <v>46.98943184830235</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>23.11873169100998</v>
+        <v>10.30688058481003</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.9593717187651564</v>
+        <v>1.961864591148281</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>3.67400421918699</v>
+        <v>0.3954174746544863</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>7856</v>
+        <v>7736</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>漢測</t>
+          <t>虎山</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>512.9813849548048</v>
+        <v>575.100054659503</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>4280</v>
+        <v>71</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,49 +2619,49 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>43.85911296091369</v>
+        <v>61.10828254975204</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>13.90262359320025</v>
+        <v>19.93416092877733</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.9347270074433376</v>
+        <v>5.887445329760578</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-94.77249416295854</v>
+        <v>0.2130554458701181</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, invest_trust_buy_2d, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>7768</v>
+        <v>6855</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>頌勝科技</t>
+          <t>數泓科</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>508.3242387885813</v>
+        <v>565.1251476897216</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>306.5</v>
+        <v>113.5</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>59.59556367901624</v>
+        <v>52.5368553202456</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>25.56607285530211</v>
+        <v>8.529426172054634</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.546186413105367</v>
+        <v>0.2711995738292411</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>3.756040046416675</v>
+        <v>2.269884417022136</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6838</v>
+        <v>6885</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>台新藥</t>
+          <t>全福生技</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>507.8359140586457</v>
+        <v>541.5986477092932</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>25.3</v>
+        <v>29.3</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>59.26964326668524</v>
+        <v>57.22410343891123</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>34.89083337589996</v>
+        <v>57.97306780459669</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.9233380184851756</v>
+        <v>0.912802479979175</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.122407696830194</v>
+        <v>-0.1266333035186599</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>7610</v>
+        <v>6925</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>聯友金屬-創</t>
+          <t>意藍</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>505.5824113842716</v>
+        <v>540.3670509054161</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>1800</v>
+        <v>69.2</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>50.51457093646291</v>
+        <v>64.9124605539721</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>10.62541359668205</v>
+        <v>36.04300908481409</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.347074896845807</v>
+        <v>1.478664261791016</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-12.37492854186183</v>
+        <v>1.334178410232499</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>7734</v>
+        <v>8011</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>印能科技</t>
+          <t>台通</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>494.2764129342027</v>
+        <v>520.6329723227857</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>2790</v>
+        <v>16.1</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>50.92004585747017</v>
+        <v>53.64367241225991</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>15.4756000694491</v>
+        <v>23.61627055503247</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.6298612985967221</v>
+        <v>0.9618928450862974</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>37.88578716305595</v>
+        <v>0.0599414328452414</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>7631</v>
+        <v>7749</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>聚賢研發-創</t>
+          <t>意騰-KY</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>474.2045743569132</v>
+        <v>520.3544650161869</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>141.5</v>
+        <v>399</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>51.29962622617985</v>
+        <v>62.30496554716991</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>21.42117934420934</v>
+        <v>23.11873193299812</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.408233094846098</v>
+        <v>0.9593717187651564</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.6018390165010455</v>
+        <v>3.674004223637819</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6894</v>
+        <v>7822</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>衛司特</t>
+          <t>倍利科</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>473.087244241157</v>
+        <v>517.4019125327598</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>358</v>
+        <v>990</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>51.59352228723601</v>
+        <v>64.92407555016595</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>29.3088325270948</v>
+        <v>18.76056013532939</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.440255200733023</v>
+        <v>1.166594842358117</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.8804670968870116</v>
+        <v>17.77924075943773</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>7842</v>
+        <v>7856</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>天能綠電</t>
+          <t>漢測</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>470.3664013159105</v>
+        <v>512.9813849548048</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>97.90000000000001</v>
+        <v>4280</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,49 +2990,49 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>50.97356957051244</v>
+        <v>43.85911296091369</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>14.2866679805629</v>
+        <v>13.90262359320025</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.7128808120476132</v>
+        <v>0.9347270074433376</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M48" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.2835301423464366</v>
+        <v>-94.77249416295854</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, williams_r_recovery, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6947</v>
+        <v>7768</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>台鎔科技</t>
+          <t>頌勝科技</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>469.0101026347423</v>
+        <v>508.3242387885813</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>68.7</v>
+        <v>306.5</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>46.98943204250288</v>
+        <v>59.59556366255589</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>10.30688060365</v>
+        <v>25.56607275756292</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.961864591148281</v>
+        <v>1.546186413105367</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.3954174742539074</v>
+        <v>3.756040046973027</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>7689</v>
+        <v>6838</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>大鵬科CLMX</t>
+          <t>台新藥</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>467.5707118990067</v>
+        <v>507.8359140586457</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>164</v>
+        <v>25.3</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>48.04957874123067</v>
+        <v>59.26964331936382</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>21.33585626653348</v>
+        <v>34.89083328883849</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>3.922453783839921</v>
+        <v>0.9233380184851756</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>1.429365697371967</v>
+        <v>0.1224076969859754</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6907</v>
+        <v>7610</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>雅特力-KY</t>
+          <t>聯友金屬-創</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>466.1381424014009</v>
+        <v>505.5824113842715</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>193.5</v>
+        <v>1800</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>54.40868112294999</v>
+        <v>50.51457093615473</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>17.03882811821394</v>
+        <v>10.62541361170762</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.168880686132186</v>
+        <v>1.347074896845807</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>1.410241633802185</v>
+        <v>-12.37492854183945</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6840</v>
+        <v>6906</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>東研信超</t>
+          <t>現觀科</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>465.5688230882918</v>
+        <v>503.2260882308091</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>97</v>
+        <v>82.7</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>54.32084550050418</v>
+        <v>54.08258285610042</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>33.71737480142559</v>
+        <v>42.13840591980502</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.6009264275647326</v>
+        <v>0.420014159747699</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-1.135334791872496</v>
+        <v>-0.1984068737260058</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6997</v>
+        <v>7734</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>博弘</t>
+          <t>印能科技</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>462.970662970519</v>
+        <v>494.2764129342033</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>66.5</v>
+        <v>2790</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>52.35558477731319</v>
+        <v>50.92004575574776</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>9.172802507995277</v>
+        <v>15.47560015137603</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.8171197004526388</v>
+        <v>0.6298612985967221</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.1824887972908131</v>
+        <v>37.88578718308462</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6887</v>
+        <v>7765</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>寶綠特-KY</t>
+          <t>中華資安</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>457.2958567043118</v>
+        <v>478.4887479849368</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>37.55</v>
+        <v>229</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>47.93911941980896</v>
+        <v>46.68592903943474</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>38.4306351746376</v>
+        <v>36.12390713634433</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>3.634992781389065</v>
+        <v>0.8362460530103862</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.06970695153757921</v>
+        <v>-0.7056321109028572</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>7823</v>
+        <v>7631</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>奧義賽博-KY創</t>
+          <t>聚賢研發-創</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>437.2969825182626</v>
+        <v>474.2045743569132</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>79.90000000000001</v>
+        <v>141.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>43.891638221426</v>
+        <v>51.29962639612063</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>13.17473975924405</v>
+        <v>21.42117936570212</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.844166781023961</v>
+        <v>1.408233094846098</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.028323695147727</v>
+        <v>0.6018390169461698</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>7828</v>
+        <v>6894</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>創新服務</t>
+          <t>衛司特</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>430.8356823471958</v>
+        <v>473.087244241157</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>1840</v>
+        <v>358</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>47.4304434303676</v>
+        <v>51.59352224753056</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>20.14452591540282</v>
+        <v>29.30883249140049</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.5468453975460187</v>
+        <v>1.440255200733023</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-25.29996355048055</v>
+        <v>-0.8804670965532138</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6869</v>
+        <v>7842</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>雲豹能源</t>
+          <t>天能綠電</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>424.2537153968557</v>
+        <v>470.3664013159105</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>68.59999999999999</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>51.80077651229838</v>
+        <v>50.97356970380722</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>23.27768403019314</v>
+        <v>14.28666799084457</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1.09060451815146</v>
+        <v>0.7128808120476132</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.3404186502589116</v>
+        <v>-0.2835301427915176</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, williams_r_recovery, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>7805</v>
+        <v>7689</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>威聯通</t>
+          <t>大鵬科CLMX</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>419.6643590856605</v>
+        <v>467.5707118990067</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>498.5</v>
+        <v>164</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>39.05328087785723</v>
+        <v>48.04957874123067</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>32.56886849998555</v>
+        <v>21.33585626653348</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.27944687434345</v>
+        <v>3.922453783839921</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>4.279575406601236</v>
+        <v>1.429365697371967</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6877</v>
+        <v>6840</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>鏵友益</t>
+          <t>東研信超</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>417.3598869059731</v>
+        <v>465.5688230882918</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>145.5</v>
+        <v>97</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>67.50955617230422</v>
+        <v>54.32084552431302</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>25.53772624167839</v>
+        <v>33.7173748503231</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>7.226308264503901</v>
+        <v>0.6009264275647326</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>3.606732784322306</v>
+        <v>-1.135334792050535</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>7714</v>
+        <v>7770</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>創泓科技</t>
+          <t>君曜</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>412.8522966598868</v>
+        <v>464.8287290563546</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>169.5</v>
+        <v>42</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>50.72895779420779</v>
+        <v>58.34035402415856</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>21.80424914112011</v>
+        <v>11.93559741018042</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.2781363906016436</v>
+        <v>1.194996607273681</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.392316096467167</v>
+        <v>0.4225866543182692</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>8011</v>
+        <v>6997</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>台通</t>
+          <t>博弘</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>410.6329723227874</v>
+        <v>462.970662970519</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>16.1</v>
+        <v>66.5</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>53.64367249595041</v>
+        <v>52.35558477571644</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>23.61627036010159</v>
+        <v>9.172802529496163</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.9618928450862974</v>
+        <v>0.8171197004526388</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.0599414327339701</v>
+        <v>0.1824887972908131</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>7747</v>
+        <v>6887</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>昕奇雲端</t>
+          <t>寶綠特-KY</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>407.6316980609668</v>
+        <v>457.2958567043117</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>111.5</v>
+        <v>37.55</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>51.56370689505235</v>
+        <v>47.93911941980896</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>6.501811409781968</v>
+        <v>38.43063545127027</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.06316980609668379</v>
+        <v>3.634992781389065</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>1.38293578446916</v>
+        <v>-0.0697069520716829</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>7750</v>
+        <v>7786</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>新代</t>
+          <t>東方風能</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>400.2771295109973</v>
+        <v>455.389423534107</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>2070</v>
+        <v>120.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>50.64844046897884</v>
+        <v>54.08078337113834</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>19.02153798152599</v>
+        <v>12.67240947151919</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.356261168170537</v>
+        <v>1.827125573531982</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>6.49095634340371</v>
+        <v>0.4784264383457014</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, williams_r_recovery</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6906</v>
+        <v>6909</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>現觀科</t>
+          <t>創控</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>393.2260882308092</v>
+        <v>451.3229801017778</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>82.7</v>
+        <v>43.95</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>54.08258270651132</v>
+        <v>59.48692408178963</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>42.13840596754601</v>
+        <v>23.30581686931073</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.420014159747699</v>
+        <v>1.285062329627247</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.198406873392186</v>
+        <v>0.321886239089197</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>7822</v>
+        <v>6994</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>倍利科</t>
+          <t>富威電力</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>387.4019125327598</v>
+        <v>450.3962844438366</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>990</v>
+        <v>31.95</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>64.9240754573763</v>
+        <v>54.10396132483011</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>18.76056013528466</v>
+        <v>41.23513376437046</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.166594842358117</v>
+        <v>3.237469980239267</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>17.77924076233076</v>
+        <v>0.7040604415202001</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>7721</v>
+        <v>7823</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>微程式</t>
+          <t>奧義賽博-KY創</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>382.5374971725246</v>
+        <v>437.2969825182626</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>63</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>56.26934495118969</v>
+        <v>43.891638221426</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>17.40868193548419</v>
+        <v>13.17473975924405</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.4812765409857161</v>
+        <v>1.844166781023961</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.3656402050635201</v>
+        <v>-0.028323695147727</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6949</v>
+        <v>7828</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>沛爾生醫-創</t>
+          <t>創新服務</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>382.3646328604741</v>
+        <v>430.8356823471962</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>47.6</v>
+        <v>1840</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>25.85853939523183</v>
+        <v>47.43044343583516</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>44.90722788480105</v>
+        <v>20.14452584224524</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.4198290597203436</v>
+        <v>0.5468453975460187</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>21.62596206626037</v>
+        <v>-25.29996355237196</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6988</v>
+        <v>6869</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>威力暘-創</t>
+          <t>雲豹能源</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>369.2288601437388</v>
+        <v>424.2537153968556</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>11.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>47.71950275769792</v>
+        <v>51.8007763761424</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>10.29226819391988</v>
+        <v>23.27768440285838</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.3420026248701459</v>
+        <v>1.09060451815146</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.0166487430266554</v>
+        <v>0.3404186511490772</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>7765</v>
+        <v>7805</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>中華資安</t>
+          <t>威聯通</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>368.4887479849368</v>
+        <v>419.6643590856605</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>229</v>
+        <v>498.5</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>46.68592906461021</v>
+        <v>39.05328074173782</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>36.12390713634433</v>
+        <v>32.56886855050009</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.8362460530103862</v>
+        <v>1.27944687434345</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.7056321110140984</v>
+        <v>4.279575409271715</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6855</v>
+        <v>7714</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>數泓科</t>
+          <t>創泓科技</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>365.1251476897216</v>
+        <v>412.8522966598868</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>113.5</v>
+        <v>169.5</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>52.53685531906516</v>
+        <v>50.72895773403928</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>8.529426154296999</v>
+        <v>21.80424911910738</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.2711995738292411</v>
+        <v>0.2781363906016436</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>2.269884417244678</v>
+        <v>-0.3923160956882525</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>8033</v>
+        <v>7747</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>雷虎</t>
+          <t>昕奇雲端</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>356.9317167150122</v>
+        <v>407.6316980609668</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>173</v>
+        <v>111.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>47.62985771230803</v>
+        <v>51.56370689505235</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>7.688385507058548</v>
+        <v>6.501811331184597</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.8674172033869811</v>
+        <v>0.06316980609668379</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.9292803467413098</v>
+        <v>1.382935784024079</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>7786</v>
+        <v>7818</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>東方風能</t>
+          <t>溢泰實業</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>345.3894235341071</v>
+        <v>398.5963966783975</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>120.5</v>
+        <v>60</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>54.08078318929242</v>
+        <v>38.281572039362</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>12.67240947151919</v>
+        <v>15.93352785035156</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1.827125573531982</v>
+        <v>1.581488118585972</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.4784264390133315</v>
+        <v>0.1450506822091116</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>7740</v>
+        <v>7547</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>熙特爾-創</t>
+          <t>碩網</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>337.3043290294347</v>
+        <v>395.5996729043338</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>102.5</v>
+        <v>63.7</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>26.26951715687841</v>
+        <v>75.21849845792131</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>27.96319158047621</v>
+        <v>26.75036331454576</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.9865695512264678</v>
+        <v>0.8599672904333832</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-1.355270637844284</v>
+        <v>1.554367979959179</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6899</v>
+        <v>7760</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>創為精密</t>
+          <t>享溫馨</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>336.1257620999507</v>
+        <v>386.5605191799971</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>49.6</v>
+        <v>32.8</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>45.8628801256213</v>
+        <v>48.19738189106407</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>23.03915508239619</v>
+        <v>27.0128957517835</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.2192094416844211</v>
+        <v>0.5279567094749159</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.0463852027878294</v>
+        <v>-0.0013509944407182</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6910</v>
+        <v>7721</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>德鴻</t>
+          <t>微程式</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>332.5027098618698</v>
+        <v>382.5374971725247</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>25.8</v>
+        <v>63</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>53.08052720691303</v>
+        <v>56.26934485679294</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>34.6530087831582</v>
+        <v>17.40868182126113</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.9224713994217024</v>
+        <v>0.4812765409857161</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.0929953148417363</v>
+        <v>0.365640205174794</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6965</v>
+        <v>6949</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>中傑-KY</t>
+          <t>沛爾生醫-創</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>328.784443269672</v>
+        <v>382.3646328604741</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>59.8</v>
+        <v>47.6</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>15.34647843053739</v>
+        <v>25.85853922429519</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>50.73218009387298</v>
+        <v>44.90722781213587</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>2.2784443269672</v>
+        <v>0.4198290597203436</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.8466434855537219</v>
+        <v>21.62596207960928</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>7770</v>
+        <v>6955</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>君曜</t>
+          <t>邦睿生技-創</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>324.8287290563547</v>
+        <v>373.4199687658717</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>42</v>
+        <v>93.5</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>58.34035410193479</v>
+        <v>48.76054156668962</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>11.93559710507301</v>
+        <v>6.002550342667174</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.194996607273681</v>
+        <v>1.874195614193252</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.4225866538286802</v>
+        <v>1.177950382471566</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6909</v>
+        <v>7728</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>創控</t>
+          <t>光焱科技</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>311.3229801017767</v>
+        <v>372.87947624522</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>43.95</v>
+        <v>636</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>59.4869239596737</v>
+        <v>53.92310408590139</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>23.30581677880324</v>
+        <v>20.08822162867068</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.285062329627247</v>
+        <v>0.4992587856532587</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.3218862396455544</v>
+        <v>3.868763345152701</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6865</v>
+        <v>6988</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>偉康科技</t>
+          <t>威力暘-創</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>310.2682566313413</v>
+        <v>369.2288601437388</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>27.7</v>
+        <v>11.7</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>54.49083594827387</v>
+        <v>47.71950284574793</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>14.00401782680619</v>
+        <v>10.29226814742274</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.6673150744807038</v>
+        <v>0.3420026248701459</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>1</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.1045208363792318</v>
+        <v>-0.016648743015529</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6914</v>
+        <v>8033</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>阜爾運通</t>
+          <t>雷虎</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>307.3553926684051</v>
+        <v>366.9317167150122</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>118.5</v>
+        <v>173</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>25.25864815801893</v>
+        <v>47.62985766826798</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>41.72102800734514</v>
+        <v>7.688385451552523</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>2.621264124170746</v>
+        <v>0.8674172033869811</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.6429522813348498</v>
+        <v>0.9292803469638472</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6918</v>
+        <v>7740</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>愛派司</t>
+          <t>熙特爾-創</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>305.334289698417</v>
+        <v>357.3043290294347</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>73.8</v>
+        <v>102.5</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>44.67582187489699</v>
+        <v>26.26951680705258</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>30.84410517710434</v>
+        <v>27.96319166846101</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.6544971238557292</v>
+        <v>0.9865695512264678</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.1951011561749865</v>
+        <v>-1.355270635730128</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>7715</v>
+        <v>6899</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>裕山</t>
+          <t>創為精密</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>303.6978613178716</v>
+        <v>336.1257620999509</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>26.95</v>
+        <v>49.6</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>35.81704418543261</v>
+        <v>45.86288003105238</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>25.73941012672446</v>
+        <v>23.03915512314044</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>3.510917949215509</v>
+        <v>0.2192094416844211</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.1154495908234501</v>
+        <v>0.0463852028545905</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6921</v>
+        <v>6910</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>嘉雨思-創</t>
+          <t>德鴻</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>299.0958523679938</v>
+        <v>332.5027098618688</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>66</v>
+        <v>25.8</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>52.22756092508412</v>
+        <v>53.0805268251682</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>18.21463101731072</v>
+        <v>34.65300899712912</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.6473852153432534</v>
+        <v>0.9224713994217024</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.3941412578122081</v>
+        <v>0.0929953151199151</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>7839</v>
+        <v>6965</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>達人網</t>
+          <t>中傑-KY</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>298.6507655562196</v>
+        <v>328.784443269672</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>43</v>
+        <v>59.8</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>42.34271810407866</v>
+        <v>15.34647841353299</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>31.43907772860648</v>
+        <v>50.73218003707707</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1.120971508640822</v>
+        <v>2.2784443269672</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.0419065995485154</v>
+        <v>-0.8466434855537219</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6955</v>
+        <v>7769</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>邦睿生技-創</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>298.4199687658717</v>
+        <v>325.6345150650941</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>93.5</v>
+        <v>5815</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>48.7605416252825</v>
+        <v>45.47316928967819</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>6.002550342667175</v>
+        <v>12.07167041681758</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.874195614193252</v>
+        <v>0.7353145706395562</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>1.177950381692666</v>
+        <v>-51.91535867947115</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6928</v>
+        <v>6862</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>攸泰科技</t>
+          <t>三集瑞-KY</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>293.7513071229351</v>
+        <v>322.285472652764</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>45.7</v>
+        <v>140.5</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>42.327313165034</v>
+        <v>52.52036114945232</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>10.47287102431336</v>
+        <v>16.0490176818344</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.82757857825762</v>
+        <v>0.9461189264503448</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.0042672926328017</v>
+        <v>1.134779948687898</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6958</v>
+        <v>6921</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>日盛台駿</t>
+          <t>嘉雨思-創</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>291.1389599358515</v>
+        <v>319.0958523679938</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>16.65</v>
+        <v>66</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>37.17430861550238</v>
+        <v>52.22756092508412</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>22.99451488462034</v>
+        <v>18.21463101731072</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>2.022905282211704</v>
+        <v>0.6473852153432534</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.0511762301925108</v>
+        <v>0.3941412578122081</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6863</v>
+        <v>6865</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>永道-KY</t>
+          <t>偉康科技</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>289.4638650630681</v>
+        <v>310.2682566313414</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>96.09999999999999</v>
+        <v>27.7</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>38.98090446776428</v>
+        <v>54.49083611107126</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>23.94349368276087</v>
+        <v>14.00401778224602</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.4781015084968927</v>
+        <v>0.6673150744807038</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.589004289073344</v>
+        <v>-0.1045208370691133</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>7818</v>
+        <v>6914</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>溢泰實業</t>
+          <t>阜爾運通</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>288.5963966783973</v>
+        <v>307.3553926684052</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>60</v>
+        <v>118.5</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>38.28157307428947</v>
+        <v>25.25864822831855</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>15.93352757369791</v>
+        <v>41.72102826544743</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.581488118585972</v>
+        <v>2.621264124170746</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.1450506818752963</v>
+        <v>0.6429522807784993</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>7820</v>
+        <v>6918</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>立盈</t>
+          <t>愛派司</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>279.2297110305968</v>
+        <v>305.3342896984171</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>111</v>
+        <v>73.8</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>51.3806763782009</v>
+        <v>44.67582152702177</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>9.834581571001715</v>
+        <v>30.84410518450714</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.3424329647023178</v>
+        <v>0.6544971238557292</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>1.639403472157287</v>
+        <v>-0.1951011557521554</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>7760</v>
+        <v>7715</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>享溫馨</t>
+          <t>裕山</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>276.5605191799969</v>
+        <v>303.6978613178722</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>32.8</v>
+        <v>26.95</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>48.19738233263286</v>
+        <v>35.81704409592933</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>27.01289574934619</v>
+        <v>25.73941012030242</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.5279567094749159</v>
+        <v>3.510917949215509</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.0013509944740976</v>
+        <v>0.1154495909347205</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6919</v>
+        <v>7839</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>達人網</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>274.1832852185881</v>
+        <v>298.6507655562196</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>78.8</v>
+        <v>43</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>35.1986464470899</v>
+        <v>42.34271810407866</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>29.20772631668952</v>
+        <v>31.43907747549298</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.6428065371522707</v>
+        <v>1.120971508640822</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.4638336297645491</v>
+        <v>0.0419065995485154</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>7855</v>
+        <v>6928</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>和運租車</t>
+          <t>攸泰科技</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>273.1157679409177</v>
+        <v>293.751307122935</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>41.3</v>
+        <v>45.7</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>16.70117690739863</v>
+        <v>42.32731305388094</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>60.24921237135119</v>
+        <v>10.47287098868076</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.4985227444034151</v>
+        <v>1.82757857825762</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>1.02743824523238</v>
+        <v>-0.0042672926550533</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6994</v>
+        <v>6958</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>富威電力</t>
+          <t>日盛台駿</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>265.3962844438366</v>
+        <v>291.1389599358513</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>31.95</v>
+        <v>16.65</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>54.10396128500201</v>
+        <v>37.17430875919096</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>41.23513376845493</v>
+        <v>22.99451489584539</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>3.237469980239267</v>
+        <v>2.022905282211704</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.7040604421878278</v>
+        <v>-0.0511762302481494</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, adx_trending, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>8034</v>
+        <v>6863</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>榮群</t>
+          <t>永道-KY</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>264.5195924834071</v>
+        <v>289.4638650630681</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>19.75</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>46.13774257173393</v>
+        <v>38.98090458591047</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>18.18449510829973</v>
+        <v>23.94349368276087</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.6022697741712375</v>
+        <v>0.4781015084968927</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.0649685799580188</v>
+        <v>0.5890042886282361</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>7821</v>
+        <v>7820</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>神數</t>
+          <t>立盈</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>259.1277653455027</v>
+        <v>279.2297110305968</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>35.15</v>
+        <v>111</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>19.57921301427189</v>
+        <v>51.38067637442622</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>32.28582865528548</v>
+        <v>9.834581594143144</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.8127765345502668</v>
+        <v>0.3424329647023178</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.3069310982457093</v>
+        <v>1.639403472157287</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>7547</v>
+        <v>6919</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>碩網</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>255.5996729043338</v>
+        <v>274.1832852185881</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>63.7</v>
+        <v>78.8</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>75.21849836748292</v>
+        <v>35.19864634387542</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>26.75036336055005</v>
+        <v>29.20772633234956</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.8599672904333832</v>
+        <v>0.6428065371522707</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>1.554367979291554</v>
+        <v>0.4638336304321733</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6923</v>
+        <v>7855</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>中台</t>
+          <t>和運租車</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>254.918661009584</v>
+        <v>273.1157679409177</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>73.5</v>
+        <v>41.3</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>35.2872623651803</v>
+        <v>16.70117690739863</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>15.74678547049428</v>
+        <v>60.24921237135119</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.348407970020327</v>
+        <v>0.4985227444034151</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.2425187479852032</v>
+        <v>1.02743824523238</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6873</v>
+        <v>8034</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>泓德能源</t>
+          <t>榮群</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>250.9491276567157</v>
+        <v>264.519592483405</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>65.90000000000001</v>
+        <v>19.75</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>34.07294230347765</v>
+        <v>46.13774274376795</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>15.48942221533155</v>
+        <v>18.18449511758171</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.997140616204274</v>
+        <v>0.6022697741712375</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.0682075561861967</v>
+        <v>-0.0649685799914024</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>7769</v>
+        <v>7821</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>神數</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>250.6345150650903</v>
+        <v>259.1277653455027</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>5815</v>
+        <v>35.15</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>45.47316927695172</v>
+        <v>19.57921348430179</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>12.07167029816962</v>
+        <v>32.28582865528548</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.7353145706395562</v>
+        <v>0.8127765345502668</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-51.91535866723126</v>
+        <v>-0.3069310983569848</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6934</v>
+        <v>6923</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>心誠鎂</t>
+          <t>中台</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>246.3467533171204</v>
+        <v>254.9186610095854</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>74.40000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>49.38533951931444</v>
+        <v>35.28726256305939</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>17.65851375204889</v>
+        <v>15.74678550118629</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.387015189881113</v>
+        <v>1.348407970020327</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.0533750790692452</v>
+        <v>-0.2425187479852032</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>7780</v>
+        <v>6873</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>大研生醫*</t>
+          <t>泓德能源</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>245.4923698281728</v>
+        <v>250.9491276567157</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>15.8</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>34.19431654054078</v>
+        <v>34.07294249791927</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>18.26583289924888</v>
+        <v>15.48942216163564</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>2.673867090785175</v>
+        <v>1.997140616204274</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.0109245102393504</v>
+        <v>0.0682075540720417</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>7753</v>
+        <v>6934</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>星亞</t>
+          <t>心誠鎂</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>239.5829989156382</v>
+        <v>246.3467533171204</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>35.65</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>40.3737612501729</v>
+        <v>49.38533950418395</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>12.26053923239624</v>
+        <v>17.6585137800822</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>3.070364018454552</v>
+        <v>1.387015189881113</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.08408947808627271</v>
+        <v>-0.0533750790024793</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6854</v>
+        <v>7780</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>錼創科技-KY創</t>
+          <t>大研生醫*</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>239.282033162393</v>
+        <v>245.4923698281725</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>93</v>
+        <v>15.8</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>50.31633143310789</v>
+        <v>34.19432414526406</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>15.70117245918074</v>
+        <v>18.26582816928496</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>1.009402906254464</v>
+        <v>2.673867090785175</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.5718407110603745</v>
+        <v>-0.0109245143005453</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>7728</v>
+        <v>7753</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>光焱科技</t>
+          <t>星亞</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>232.8794762452198</v>
+        <v>239.5829989156382</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>636</v>
+        <v>35.65</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>53.92310405800724</v>
+        <v>40.3737633527994</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>20.088221479238</v>
+        <v>12.2605392347178</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.4992587856532587</v>
+        <v>3.070364018454552</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>3.868763346265408</v>
+        <v>0.084089478219804</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6951</v>
+        <v>6854</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>青新-創</t>
+          <t>錼創科技-KY創</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>232.0768668099032</v>
+        <v>239.282033162393</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>69.09999999999999</v>
+        <v>93</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>33.30884643668387</v>
+        <v>50.31633164517842</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>29.03892786704596</v>
+        <v>15.7011724598259</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1.019093325692819</v>
+        <v>1.009402906254464</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.0149281047011843</v>
+        <v>0.5718407110603745</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6952</v>
+        <v>6951</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>大武山</t>
+          <t>青新-創</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>229.586625154558</v>
+        <v>232.0768668099033</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>38.75</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>51.99537096596453</v>
+        <v>33.30884637691506</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>10.46754450012235</v>
+        <v>29.03892782133607</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1.151411430613281</v>
+        <v>1.019093325692819</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.5182944109166372</v>
+        <v>0.0149281047234556</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>7704</v>
+        <v>6952</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>明遠精密</t>
+          <t>大武山</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>219.9759459179613</v>
+        <v>229.586625154558</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>60.4</v>
+        <v>38.75</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>43.97125325231462</v>
+        <v>51.99537094727162</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>17.36148862305404</v>
+        <v>10.46754455704112</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>1.226392638235946</v>
+        <v>1.151411430613281</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.1254817780710715</v>
+        <v>0.518294411083537</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>8024</v>
+        <v>7704</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>佑華</t>
+          <t>明遠精密</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>219.4797789551383</v>
+        <v>219.9759459179613</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>12.4</v>
+        <v>60.4</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>35.74408357075963</v>
+        <v>43.9712530811115</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>13.99968110670225</v>
+        <v>17.36148861918517</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>2.153021811089534</v>
+        <v>1.226392638235946</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.0061354111673634</v>
+        <v>-0.1254817780043101</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>7738</v>
+        <v>8024</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>東聯互動</t>
+          <t>佑華</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>217.9397309952869</v>
+        <v>219.4797789551383</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>155</v>
+        <v>12.4</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>32.96547690699761</v>
+        <v>35.74408355527223</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>17.48347585732241</v>
+        <v>13.99968115139405</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>1.120987470756192</v>
+        <v>2.153021811089534</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.5145663910773743</v>
+        <v>0.0061354111673634</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6862</v>
+        <v>7738</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>三集瑞-KY</t>
+          <t>東聯互動</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>212.285472652764</v>
+        <v>217.9397309952877</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>140.5</v>
+        <v>155</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>52.52036117315154</v>
+        <v>32.96547561757785</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>16.04901763054743</v>
+        <v>17.48347595349634</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.9461189264503448</v>
+        <v>1.120987470756192</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,11 +6347,11 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>1.134779948465357</v>
+        <v>-0.5145663871828581</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>209.3357448955363</v>
+        <v>209.3357448955364</v>
       </c>
       <c r="E112" s="2" t="n">
         <v>23.75</v>
@@ -6382,10 +6382,10 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>34.46865691387281</v>
+        <v>34.46865693257658</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>28.69574749344851</v>
+        <v>28.69574750166077</v>
       </c>
       <c r="J112" s="2" t="n">
         <v>0.7591123001741414</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.0419189261354097</v>
+        <v>-0.0419189261687913</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6410,21 +6410,21 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6969</v>
+        <v>7722</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>成信實業*-創</t>
+          <t>LINEPAY</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>205.1045959035375</v>
+        <v>205.2912635920591</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>31.3</v>
+        <v>262</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>45.37584386861121</v>
+        <v>41.87264869079269</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>14.65175474383628</v>
+        <v>14.99475733239701</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>1.060538913364717</v>
+        <v>0.7577535231751622</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.2711884393476007</v>
+        <v>0.4732832285611854</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6996</v>
+        <v>6969</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>力領科技</t>
+          <t>成信實業*-創</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>203.4417212286862</v>
+        <v>205.1045959035375</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>165.5</v>
+        <v>31.3</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>37.53370849254853</v>
+        <v>45.37584386861121</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>16.26239107013792</v>
+        <v>14.65175482029447</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>2.357073643410853</v>
+        <v>1.060538913364717</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.033831326556132</v>
+        <v>-0.2711884399595899</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>7732</v>
+        <v>6996</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>金興精密</t>
+          <t>力領科技</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>197.195580746007</v>
+        <v>203.4417212286859</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>32.7</v>
+        <v>165.5</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>50.96948703735196</v>
+        <v>37.53370842272009</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>8.631220550566542</v>
+        <v>16.26239090449632</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>3.732729500905127</v>
+        <v>2.357073643410853</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.7489101313583377</v>
+        <v>-0.0338313257772351</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6569,21 +6569,21 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6913</v>
+        <v>7732</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>鴻呈</t>
+          <t>金興精密</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>193.2928681123322</v>
+        <v>197.1955807460069</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>130</v>
+        <v>32.7</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>44.90267646189656</v>
+        <v>50.96948702274106</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>16.5735088515344</v>
+        <v>8.63122072542593</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.524586863853795</v>
+        <v>3.732729500905127</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.2196977261827313</v>
+        <v>0.7489101315363762</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6890</v>
+        <v>6913</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>鴻呈</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>192.2475017424321</v>
+        <v>193.2928681123322</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>37.08142304990879</v>
+        <v>44.90267623186716</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>9.526776355908584</v>
+        <v>16.57350893723131</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.4116022895179612</v>
+        <v>0.524586863853795</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.5686659182192448</v>
+        <v>0.2196977275179712</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>7803</v>
+        <v>6890</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>雲象科技-創</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>187.9161562290197</v>
+        <v>192.247501742432</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>17.65</v>
+        <v>147</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,16 +6700,16 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>34.81052233953248</v>
+        <v>37.08142326175262</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>13.81497010175378</v>
+        <v>9.526776391492318</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>2.039949619159412</v>
+        <v>0.4116022895179612</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.0662337930497001</v>
+        <v>0.5686659171065074</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>7722</v>
+        <v>7803</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>LINEPAY</t>
+          <t>雲象科技-創</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>185.2912635920591</v>
+        <v>187.9161562290197</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>262</v>
+        <v>17.65</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>41.87264863924466</v>
+        <v>34.81052242406044</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>14.99475733754756</v>
+        <v>13.81497023052352</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.7577535231751622</v>
+        <v>2.039949619159412</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,11 +6771,11 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.473283230341476</v>
+        <v>-0.0662337930497001</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6792,7 @@
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>175.6020129472299</v>
+        <v>175.60201294723</v>
       </c>
       <c r="E120" s="2" t="n">
         <v>36.15</v>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>53.69456734066798</v>
+        <v>53.69456788980087</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>15.40053606625212</v>
+        <v>15.40053613255546</v>
       </c>
       <c r="J120" s="2" t="n">
         <v>0.6859279818236542</v>
@@ -6824,7 +6824,7 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.1662259804244961</v>
+        <v>0.1662259802575872</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
@@ -6859,10 +6859,10 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>29.50076261173044</v>
+        <v>29.50076264177495</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>12.80730918469835</v>
+        <v>12.80730923896006</v>
       </c>
       <c r="J121" s="2" t="n">
         <v>1.237619662501298</v>
@@ -6912,16 +6912,16 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>47.72247913640815</v>
+        <v>47.72247901775064</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>19.15065594113628</v>
+        <v>19.15065595844952</v>
       </c>
       <c r="J122" s="2" t="n">
         <v>2.343442094065535</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L122" s="2" t="n">
         <v>0</v>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>42.2161922019971</v>
+        <v>42.21619198449877</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>15.26753796674421</v>
+        <v>15.26753796436698</v>
       </c>
       <c r="J123" s="2" t="n">
         <v>0.912498411012425</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.2514477436925024</v>
+        <v>0.2514477442043472</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -7018,16 +7018,16 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>44.42596726313179</v>
+        <v>44.42596724420483</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>10.67599303488965</v>
+        <v>10.67599305639681</v>
       </c>
       <c r="J124" s="2" t="n">
         <v>1.422469808547936</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L124" s="2" t="n">
         <v>0</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.0155142752972814</v>
+        <v>0.0155142751414986</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7071,10 +7071,10 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>33.68815871215747</v>
+        <v>33.6881586155731</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>17.88468715399553</v>
+        <v>17.8846872651936</v>
       </c>
       <c r="J125" s="2" t="n">
         <v>1.30049579169536</v>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>46.43068928085453</v>
+        <v>46.43068925833035</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>19.8273150694978</v>
+        <v>19.82731506433833</v>
       </c>
       <c r="J126" s="2" t="n">
         <v>0.7810899379145609</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.5747307071609097</v>
+        <v>-0.5747307069205675</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7177,10 +7177,10 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>32.81183235667136</v>
+        <v>32.81183223676591</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>19.65703498409534</v>
+        <v>19.65703495087072</v>
       </c>
       <c r="J127" s="2" t="n">
         <v>1.35623138168057</v>
@@ -7195,7 +7195,7 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-1.308085161541213</v>
+        <v>-1.308085161162886</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
@@ -7230,16 +7230,16 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>27.33216400078457</v>
+        <v>27.33216430775191</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>18.84936981063987</v>
+        <v>18.84936981619942</v>
       </c>
       <c r="J128" s="2" t="n">
         <v>1.197574656909231</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L128" s="2" t="n">
         <v>0</v>
@@ -7248,7 +7248,7 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>-0.2458316458486336</v>
+        <v>-0.2458316460711787</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
